--- a/InputData/hydgn/BSfHPbP/BAU Subsidy for Hydgn Prod by Pathway.xlsx
+++ b/InputData/hydgn/BSfHPbP/BAU Subsidy for Hydgn Prod by Pathway.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\hydgn\BSfHPbP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74F3C4B-C72E-4F62-AD8D-71E7DDB3ED2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01940525-DDC8-4DBE-919C-ECDC8C180339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22170" yWindow="2010" windowWidth="21120" windowHeight="14655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="73">
   <si>
     <t>Source:</t>
   </si>
@@ -124,6 +124,144 @@
   </si>
   <si>
     <t>BSfHPbP BAU Subsidy for Hydrogen Production by Pathway</t>
+  </si>
+  <si>
+    <t>Last plant in-service year eligible: green (45V)</t>
+  </si>
+  <si>
+    <t>2026-10-23 update (One Big Beautiful Bill Act, Pub. L. 119-21, July 4, 2025)</t>
+  </si>
+  <si>
+    <t>Green (45V): OBBBA sec. 70511 moved the 45V construction-start deadline from before 2033 to before</t>
+  </si>
+  <si>
+    <t>January 1, 2028 (26 U.S.C. 45V(c)(3)(C), checked on the current U.S. Code text). EPS pays this subsidy by</t>
+  </si>
+  <si>
+    <t>the year a plant enters service and locks it in for HPSD years (Hydrogen Production Subsidies for</t>
+  </si>
+  <si>
+    <t>Newly Built Plants and its DELAY FIXED expiry), so the row is the credit for plants ENTERING SERVICE</t>
+  </si>
+  <si>
+    <t>in each year. With construction starting by end-2027 and the IRS 4-year continuity safe harbor (not</t>
+  </si>
+  <si>
+    <t>re-checked against IRS guidance in this update), we</t>
+  </si>
+  <si>
+    <t>assume qualifying plants are in service by 2030; plants entering service from 2031 get zero. Plants</t>
+  </si>
+  <si>
+    <t>already in service keep their credit for the full 10-year period. (calcs!B15 sets the last year.)</t>
+  </si>
+  <si>
+    <t>Blue: real SMR+CCS projects mostly claim 45Q ($85/t stored, 12 years) rather than 45V, and the two</t>
+  </si>
+  <si>
+    <t>cannot be combined. 45Q requires construction to begin before January 1, 2033 (26 U.S.C. 45Q(d)(1);</t>
+  </si>
+  <si>
+    <t>OBBBA sec. 70522 changed 45Q's rates and parity but not this date). The blue row is therefore a</t>
+  </si>
+  <si>
+    <t>45Q PROXY: $0.75/kg (2022$) is about $85/t x ~8.3 kg CO2 captured per kg H2, paid for HPSD (10) years</t>
+  </si>
+  <si>
+    <t>rather than 12. It is kept to in-service year 2032 (calcs!B16), a conservative cut for a 2032</t>
+  </si>
+  <si>
+    <t>construction-start deadline. Grid electrolysis (row 2) stays 0: grid-average power is far above</t>
+  </si>
+  <si>
+    <t>the 4 kg CO2e/kg 45V ceiling.</t>
+  </si>
+  <si>
+    <t>Blue hydrogen: 45Q credit for CO2 in secure geologic storage (2026-10-23)</t>
+  </si>
+  <si>
+    <t>45Q base amount ($/t, 26 U.S.C. 45Q(b)(1)(A), tax years 2025-2026; inflation-indexed from 2027 with 2025 base)</t>
+  </si>
+  <si>
+    <t>Multiplier for prevailing wage and apprenticeship (45Q(h))</t>
+  </si>
+  <si>
+    <t>45Q amount ($/t, 2025$; indexed, so constant in real 2025$)</t>
+  </si>
+  <si>
+    <t>CPI-U annual average 2012 (BLS CUUR0000SA0)</t>
+  </si>
+  <si>
+    <t>CPI-U annual average 2025 (BLS; 11 months, October 2025 not published)</t>
+  </si>
+  <si>
+    <t>45Q amount ($/t CO2, 2012$)</t>
+  </si>
+  <si>
+    <t>CO2 captured per kg H2, from the model's own inputs (copied; update if those inputs change):</t>
+  </si>
+  <si>
+    <t>Natural gas use, SMR with CCS (BTU gas / BTU H2): hydgn/FIoHP FIoHP-ng-reforming-CCS.csv, natural gas row (1.3729 in every year)</t>
+  </si>
+  <si>
+    <t>CO2 intensity of natural gas (g CO2 / BTU): fuels/PEI PEI-IFPEI.csv, CO2 row (no improvement in PEIIR)</t>
+  </si>
+  <si>
+    <t>Capture rate: ccs/CCP CPPbHS.csv</t>
+  </si>
+  <si>
+    <t>BTU per kg H2</t>
+  </si>
+  <si>
+    <t>45Q credit ($ per kg H2, 2012$)</t>
+  </si>
+  <si>
+    <t>45Q credit ($ per BTU H2, 2012$) - used in the BSfHPbP tab</t>
+  </si>
+  <si>
+    <t>Eligibility: construction must begin before 2033-01-01 (45Q(d)(1)); IRS Notice 2020-12 sec. 7.05 continuity safe harbor</t>
+  </si>
+  <si>
+    <t>Last construction-start year</t>
+  </si>
+  <si>
+    <t>Continuity safe harbor (calendar years after construction start, Notice 2020-12 sec. 7.05)</t>
+  </si>
+  <si>
+    <t>Last plant in-service year eligible: blue (45Q: construction-start deadline + safe harbor)</t>
+  </si>
+  <si>
+    <t>Blue (revised 2026-10-23): the row is now an explicit 45Q representation, replacing the earlier $0.75/kg 45V-tier proxy.</t>
+  </si>
+  <si>
+    <t>$17/t x 5 (prevailing wage and apprenticeship) = $85/t in 2025-2026, indexed for inflation from 2027 with a 2025</t>
+  </si>
+  <si>
+    <t>base (26 U.S.C. 45Q(b)(1)(A) as amended by Pub. L. 119-21 sec. 70522, which also gave utilization/EOR the same</t>
+  </si>
+  <si>
+    <t>rate), so it is a constant $85 in 2025 dollars; converted to 2012$ with CPI-U. Times the CO2 the model captures</t>
+  </si>
+  <si>
+    <t>per kg H2 (calcs rows 26-33). Paid for 12 years (hydgn/HPSD blue row). Eligible for plants whose construction begins</t>
+  </si>
+  <si>
+    <t>before 2033 and that enter service by the IRS continuity safe harbor (6 calendar years, Notice 2020-12 sec. 7.05),</t>
+  </si>
+  <si>
+    <t>i.e. through in-service year 2038 (calcs!B16). The EPS per-ton CCS subsidy no longer pays the hydrogen sector</t>
+  </si>
+  <si>
+    <t>(bug fix B4), so 45Q is not stacked; 45V and 45Q cannot both be claimed.</t>
+  </si>
+  <si>
+    <t>Natural gas burned for capture (BTU per g CO2 captured): ccs/CC CC-EUpTHSCS natural gas row (NETL 2022); its CO2 is captured at the same rate</t>
+  </si>
+  <si>
+    <t>Capture-fuel multiplier on CO2 captured: 1 / (1 - gas for capture x CO2 intensity x capture rate)</t>
+  </si>
+  <si>
+    <t>CO2 captured (kg CO2 / kg H2), including CO2 from gas burned for capture</t>
   </si>
 </sst>
 </file>
@@ -476,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="45.85546875" customWidth="1"/>
@@ -562,6 +700,126 @@
         <v>25</v>
       </c>
     </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -570,7 +828,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:B13"/>
+  <dimension ref="A2:B39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.5703125" bestFit="1" customWidth="1"/>
@@ -667,6 +925,182 @@
       <c r="B13">
         <f>B9/B12*About!A16</f>
         <v>4.3743117043612755E-6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16">
+        <f>B36+B37</f>
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21">
+        <f>B19*B20</f>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22">
+        <v>229.59399999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23">
+        <f>AVERAGE(317.671,319.082,319.799,320.795,321.465,322.561,323.048,323.976,324.8,324.122,324.054)</f>
+        <v>321.94299999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24">
+        <f>B21*B22/B23</f>
+        <v>60.617842288852373</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27">
+        <v>1.3729</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28">
+        <v>5.3060000000000003E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30">
+        <f>B6</f>
+        <v>134510.48006</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31">
+        <f>B27*B28*B29*B30/1000*B39</f>
+        <v>8.787529361017393</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32">
+        <f>B24*B31/1000</f>
+        <v>0.53268106891481204</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33">
+        <f>B32/B30</f>
+        <v>3.9601454747407286E-6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>70</v>
+      </c>
+      <c r="B38">
+        <v>1.1575132990000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>71</v>
+      </c>
+      <c r="B39">
+        <f>1/(1-B38*B28*B29)</f>
+        <v>1.0550804843876442</v>
       </c>
     </row>
   </sheetData>
@@ -1263,101 +1697,119 @@
         <v>0</v>
       </c>
       <c r="C7" s="5">
-        <f>calcs!B7</f>
+        <f>IF(C$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>1.7497246817445102E-5</v>
       </c>
       <c r="D7" s="5">
-        <f>C7</f>
+        <f>IF(D$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>1.7497246817445102E-5</v>
       </c>
       <c r="E7" s="5">
-        <f t="shared" ref="E7:M7" si="0">D7</f>
+        <f>IF(E$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>1.7497246817445102E-5</v>
       </c>
       <c r="F7" s="5">
-        <f t="shared" si="0"/>
+        <f>IF(F$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>1.7497246817445102E-5</v>
       </c>
       <c r="G7" s="5">
-        <f t="shared" si="0"/>
+        <f>IF(G$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>1.7497246817445102E-5</v>
       </c>
       <c r="H7" s="5">
-        <f t="shared" si="0"/>
+        <f>IF(H$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>1.7497246817445102E-5</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" si="0"/>
+        <f>IF(I$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>1.7497246817445102E-5</v>
       </c>
       <c r="J7" s="5">
-        <f t="shared" si="0"/>
+        <f>IF(J$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>1.7497246817445102E-5</v>
       </c>
       <c r="K7" s="5">
-        <f t="shared" si="0"/>
+        <f>IF(K$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>1.7497246817445102E-5</v>
       </c>
       <c r="L7" s="5">
-        <f t="shared" si="0"/>
-        <v>1.7497246817445102E-5</v>
+        <f>IF(L$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
+        <v>0</v>
       </c>
       <c r="M7" s="5">
-        <f t="shared" si="0"/>
-        <v>1.7497246817445102E-5</v>
+        <f>IF(M$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
+        <v>0</v>
       </c>
       <c r="N7" s="5">
+        <f>IF(N$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>0</v>
       </c>
       <c r="O7" s="5">
+        <f>IF(O$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>0</v>
       </c>
       <c r="P7" s="5">
+        <f>IF(P$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>0</v>
       </c>
       <c r="Q7" s="5">
+        <f>IF(Q$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>0</v>
       </c>
       <c r="R7" s="5">
+        <f>IF(R$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>0</v>
       </c>
       <c r="S7" s="5">
+        <f>IF(S$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>0</v>
       </c>
       <c r="T7" s="5">
+        <f>IF(T$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>0</v>
       </c>
       <c r="U7" s="5">
+        <f>IF(U$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>0</v>
       </c>
       <c r="V7" s="5">
+        <f>IF(V$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>0</v>
       </c>
       <c r="W7" s="5">
+        <f>IF(W$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>0</v>
       </c>
       <c r="X7" s="5">
+        <f>IF(X$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>0</v>
       </c>
       <c r="Y7" s="5">
+        <f>IF(Y$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>0</v>
       </c>
       <c r="Z7" s="5">
+        <f>IF(Z$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>0</v>
       </c>
       <c r="AA7" s="5">
+        <f>IF(AA$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>0</v>
       </c>
       <c r="AB7" s="5">
+        <f>IF(AB$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>0</v>
       </c>
       <c r="AC7" s="5">
+        <f>IF(AC$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>0</v>
       </c>
       <c r="AD7" s="5">
+        <f>IF(AD$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>0</v>
       </c>
       <c r="AE7" s="5">
+        <f>IF(AE$1&lt;=calcs!$B$15,calcs!$B$7,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1369,101 +1821,119 @@
         <v>0</v>
       </c>
       <c r="C8" s="5">
-        <f>calcs!B13</f>
-        <v>4.3743117043612755E-6</v>
+        <f>IF(C$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
+        <v>3.9601454747407286E-6</v>
       </c>
       <c r="D8" s="5">
-        <f t="shared" ref="D8:M8" si="1">C8</f>
-        <v>4.3743117043612755E-6</v>
+        <f>IF(D$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
+        <v>3.9601454747407286E-6</v>
       </c>
       <c r="E8" s="5">
-        <f t="shared" si="1"/>
-        <v>4.3743117043612755E-6</v>
+        <f>IF(E$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
+        <v>3.9601454747407286E-6</v>
       </c>
       <c r="F8" s="5">
-        <f t="shared" si="1"/>
-        <v>4.3743117043612755E-6</v>
+        <f>IF(F$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
+        <v>3.9601454747407286E-6</v>
       </c>
       <c r="G8" s="5">
-        <f t="shared" si="1"/>
-        <v>4.3743117043612755E-6</v>
+        <f>IF(G$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
+        <v>3.9601454747407286E-6</v>
       </c>
       <c r="H8" s="5">
-        <f t="shared" si="1"/>
-        <v>4.3743117043612755E-6</v>
+        <f>IF(H$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
+        <v>3.9601454747407286E-6</v>
       </c>
       <c r="I8" s="5">
-        <f t="shared" si="1"/>
-        <v>4.3743117043612755E-6</v>
+        <f>IF(I$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
+        <v>3.9601454747407286E-6</v>
       </c>
       <c r="J8" s="5">
-        <f t="shared" si="1"/>
-        <v>4.3743117043612755E-6</v>
+        <f>IF(J$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
+        <v>3.9601454747407286E-6</v>
       </c>
       <c r="K8" s="5">
-        <f t="shared" si="1"/>
-        <v>4.3743117043612755E-6</v>
+        <f>IF(K$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
+        <v>3.9601454747407286E-6</v>
       </c>
       <c r="L8" s="5">
-        <f t="shared" si="1"/>
-        <v>4.3743117043612755E-6</v>
+        <f>IF(L$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
+        <v>3.9601454747407286E-6</v>
       </c>
       <c r="M8" s="5">
-        <f t="shared" si="1"/>
-        <v>4.3743117043612755E-6</v>
+        <f>IF(M$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
+        <v>3.9601454747407286E-6</v>
       </c>
       <c r="N8" s="5">
-        <v>0</v>
+        <f>IF(N$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
+        <v>3.9601454747407286E-6</v>
       </c>
       <c r="O8" s="5">
-        <v>0</v>
+        <f>IF(O$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
+        <v>3.9601454747407286E-6</v>
       </c>
       <c r="P8" s="5">
-        <v>0</v>
+        <f>IF(P$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
+        <v>3.9601454747407286E-6</v>
       </c>
       <c r="Q8" s="5">
-        <v>0</v>
+        <f>IF(Q$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
+        <v>3.9601454747407286E-6</v>
       </c>
       <c r="R8" s="5">
-        <v>0</v>
+        <f>IF(R$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
+        <v>3.9601454747407286E-6</v>
       </c>
       <c r="S8" s="5">
-        <v>0</v>
+        <f>IF(S$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
+        <v>3.9601454747407286E-6</v>
       </c>
       <c r="T8" s="5">
+        <f>IF(T$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
         <v>0</v>
       </c>
       <c r="U8" s="5">
+        <f>IF(U$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
         <v>0</v>
       </c>
       <c r="V8" s="5">
+        <f>IF(V$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
         <v>0</v>
       </c>
       <c r="W8" s="5">
+        <f>IF(W$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
         <v>0</v>
       </c>
       <c r="X8" s="5">
+        <f>IF(X$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
         <v>0</v>
       </c>
       <c r="Y8" s="5">
+        <f>IF(Y$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
         <v>0</v>
       </c>
       <c r="Z8" s="5">
+        <f>IF(Z$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
         <v>0</v>
       </c>
       <c r="AA8" s="5">
+        <f>IF(AA$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
         <v>0</v>
       </c>
       <c r="AB8" s="5">
+        <f>IF(AB$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
         <v>0</v>
       </c>
       <c r="AC8" s="5">
+        <f>IF(AC$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
         <v>0</v>
       </c>
       <c r="AD8" s="5">
+        <f>IF(AD$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
         <v>0</v>
       </c>
       <c r="AE8" s="5">
+        <f>IF(AE$1&lt;=calcs!$B$16,calcs!$B$33,0)</f>
         <v>0</v>
       </c>
     </row>
